--- a/artfynd/A 48359-2023 artfynd.xlsx
+++ b/artfynd/A 48359-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118891663</v>
+        <v>118891606</v>
       </c>
       <c r="B2" t="n">
-        <v>8416</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499858</v>
+        <v>499877</v>
       </c>
       <c r="R2" t="n">
-        <v>6808367</v>
+        <v>6808544</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118891606</v>
+        <v>118891663</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>8416</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499877</v>
+        <v>499858</v>
       </c>
       <c r="R3" t="n">
-        <v>6808544</v>
+        <v>6808367</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118890986</v>
+        <v>118891384</v>
       </c>
       <c r="B8" t="n">
-        <v>90524</v>
+        <v>78484</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500050</v>
+        <v>500131</v>
       </c>
       <c r="R8" t="n">
-        <v>6808191</v>
+        <v>6808303</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118891384</v>
+        <v>118890986</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>90524</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500131</v>
+        <v>500050</v>
       </c>
       <c r="R9" t="n">
-        <v>6808303</v>
+        <v>6808191</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118890625</v>
+        <v>118891390</v>
       </c>
       <c r="B17" t="n">
-        <v>79469</v>
+        <v>78484</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,38 +2222,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500110</v>
+        <v>500123</v>
       </c>
       <c r="R17" t="n">
-        <v>6808019</v>
+        <v>6808319</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,26 +2296,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2332,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118891390</v>
+        <v>118890625</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>79469</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,38 +2324,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jussinjärv (Jussinjärv), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500123</v>
+        <v>500110</v>
       </c>
       <c r="R18" t="n">
-        <v>6808319</v>
+        <v>6808019</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,6 +2398,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">

--- a/artfynd/A 48359-2023 artfynd.xlsx
+++ b/artfynd/A 48359-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118891606</v>
+        <v>118891677</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>90524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499877</v>
+        <v>499813</v>
       </c>
       <c r="R2" t="n">
-        <v>6808544</v>
+        <v>6808453</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118891663</v>
+        <v>118891606</v>
       </c>
       <c r="B3" t="n">
-        <v>8416</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499858</v>
+        <v>499877</v>
       </c>
       <c r="R3" t="n">
-        <v>6808367</v>
+        <v>6808544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118891617</v>
+        <v>118891663</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>8416</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499837</v>
+        <v>499858</v>
       </c>
       <c r="R4" t="n">
-        <v>6808476</v>
+        <v>6808367</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118891677</v>
+        <v>118891617</v>
       </c>
       <c r="B6" t="n">
-        <v>90524</v>
+        <v>78484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499813</v>
+        <v>499837</v>
       </c>
       <c r="R6" t="n">
-        <v>6808453</v>
+        <v>6808476</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118891442</v>
+        <v>118891395</v>
       </c>
       <c r="B7" t="n">
-        <v>78129</v>
+        <v>91779</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500091</v>
+        <v>500122</v>
       </c>
       <c r="R7" t="n">
-        <v>6808386</v>
+        <v>6808338</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118891384</v>
+        <v>118891025</v>
       </c>
       <c r="B8" t="n">
         <v>78484</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500131</v>
+        <v>500061</v>
       </c>
       <c r="R8" t="n">
-        <v>6808303</v>
+        <v>6808195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118890986</v>
+        <v>118891595</v>
       </c>
       <c r="B9" t="n">
-        <v>90524</v>
+        <v>78484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500050</v>
+        <v>499929</v>
       </c>
       <c r="R9" t="n">
-        <v>6808191</v>
+        <v>6808532</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118890866</v>
+        <v>118891497</v>
       </c>
       <c r="B10" t="n">
-        <v>91783</v>
+        <v>8416</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,38 +1508,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500089</v>
+        <v>500086</v>
       </c>
       <c r="R10" t="n">
-        <v>6808108</v>
+        <v>6808393</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118891168</v>
+        <v>118891776</v>
       </c>
       <c r="B11" t="n">
         <v>78484</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500091</v>
+        <v>500000</v>
       </c>
       <c r="R11" t="n">
-        <v>6808221</v>
+        <v>6808302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118891375</v>
+        <v>118891803</v>
       </c>
       <c r="B12" t="n">
-        <v>91779</v>
+        <v>78221</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500143</v>
+        <v>499999</v>
       </c>
       <c r="R12" t="n">
-        <v>6808303</v>
+        <v>6808280</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118891803</v>
+        <v>118891338</v>
       </c>
       <c r="B13" t="n">
-        <v>78221</v>
+        <v>91779</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499999</v>
+        <v>500148</v>
       </c>
       <c r="R13" t="n">
-        <v>6808280</v>
+        <v>6808267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118891025</v>
+        <v>118891168</v>
       </c>
       <c r="B14" t="n">
         <v>78484</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500061</v>
+        <v>500091</v>
       </c>
       <c r="R14" t="n">
-        <v>6808195</v>
+        <v>6808221</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118891134</v>
+        <v>118891390</v>
       </c>
       <c r="B15" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500077</v>
+        <v>500123</v>
       </c>
       <c r="R15" t="n">
-        <v>6808223</v>
+        <v>6808319</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118891338</v>
+        <v>118890625</v>
       </c>
       <c r="B16" t="n">
-        <v>91779</v>
+        <v>79469</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,34 +2124,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jussinjärv (Jussinjärv), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500148</v>
+        <v>500110</v>
       </c>
       <c r="R16" t="n">
-        <v>6808267</v>
+        <v>6808019</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,6 +2194,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2210,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118891390</v>
+        <v>118890866</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>91783</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,38 +2242,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jussinjärv (Jussinjärv), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500123</v>
+        <v>500089</v>
       </c>
       <c r="R17" t="n">
-        <v>6808319</v>
+        <v>6808108</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118890625</v>
+        <v>118891313</v>
       </c>
       <c r="B18" t="n">
-        <v>79469</v>
+        <v>78484</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,38 +2344,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500110</v>
+        <v>500158</v>
       </c>
       <c r="R18" t="n">
-        <v>6808019</v>
+        <v>6808271</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2398,26 +2418,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118891426</v>
+        <v>118891906</v>
       </c>
       <c r="B19" t="n">
-        <v>78221</v>
+        <v>90524</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500103</v>
+        <v>500003</v>
       </c>
       <c r="R19" t="n">
-        <v>6808366</v>
+        <v>6808192</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118891483</v>
+        <v>118891402</v>
       </c>
       <c r="B20" t="n">
         <v>78484</v>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500089</v>
+        <v>500118</v>
       </c>
       <c r="R20" t="n">
-        <v>6808383</v>
+        <v>6808352</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118891422</v>
+        <v>118891442</v>
       </c>
       <c r="B21" t="n">
-        <v>78220</v>
+        <v>78129</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500103</v>
+        <v>500091</v>
       </c>
       <c r="R21" t="n">
-        <v>6808366</v>
+        <v>6808386</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118891497</v>
+        <v>118891426</v>
       </c>
       <c r="B22" t="n">
-        <v>8416</v>
+        <v>78221</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2752,25 +2752,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500086</v>
+        <v>500103</v>
       </c>
       <c r="R22" t="n">
-        <v>6808393</v>
+        <v>6808366</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118891906</v>
+        <v>118891134</v>
       </c>
       <c r="B23" t="n">
-        <v>90524</v>
+        <v>78221</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500003</v>
+        <v>500077</v>
       </c>
       <c r="R23" t="n">
-        <v>6808192</v>
+        <v>6808223</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118891776</v>
+        <v>118891384</v>
       </c>
       <c r="B24" t="n">
         <v>78484</v>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500000</v>
+        <v>500131</v>
       </c>
       <c r="R24" t="n">
-        <v>6808302</v>
+        <v>6808303</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118891395</v>
+        <v>118891483</v>
       </c>
       <c r="B25" t="n">
-        <v>91779</v>
+        <v>78484</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,25 +3058,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500122</v>
+        <v>500089</v>
       </c>
       <c r="R25" t="n">
-        <v>6808338</v>
+        <v>6808383</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118891595</v>
+        <v>118891375</v>
       </c>
       <c r="B26" t="n">
-        <v>78484</v>
+        <v>91779</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3160,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499929</v>
+        <v>500143</v>
       </c>
       <c r="R26" t="n">
-        <v>6808532</v>
+        <v>6808303</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118891402</v>
+        <v>118890986</v>
       </c>
       <c r="B27" t="n">
-        <v>78484</v>
+        <v>90524</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,21 +3266,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500118</v>
+        <v>500050</v>
       </c>
       <c r="R27" t="n">
-        <v>6808352</v>
+        <v>6808191</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118891313</v>
+        <v>118891422</v>
       </c>
       <c r="B28" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500158</v>
+        <v>500103</v>
       </c>
       <c r="R28" t="n">
-        <v>6808271</v>
+        <v>6808366</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 48359-2023 artfynd.xlsx
+++ b/artfynd/A 48359-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118891677</v>
+        <v>118891631</v>
       </c>
       <c r="B2" t="n">
-        <v>90524</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499813</v>
+        <v>499913</v>
       </c>
       <c r="R2" t="n">
-        <v>6808453</v>
+        <v>6808448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>118891606</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118891663</v>
+        <v>118891617</v>
       </c>
       <c r="B4" t="n">
-        <v>8416</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499858</v>
+        <v>499837</v>
       </c>
       <c r="R4" t="n">
-        <v>6808367</v>
+        <v>6808476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118891631</v>
+        <v>118891677</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>90531</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499913</v>
+        <v>499813</v>
       </c>
       <c r="R5" t="n">
-        <v>6808448</v>
+        <v>6808453</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118891617</v>
+        <v>118891663</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>8416</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,38 +1095,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499837</v>
+        <v>499858</v>
       </c>
       <c r="R6" t="n">
-        <v>6808476</v>
+        <v>6808367</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118891395</v>
+        <v>118891906</v>
       </c>
       <c r="B7" t="n">
-        <v>91779</v>
+        <v>90531</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500122</v>
+        <v>500003</v>
       </c>
       <c r="R7" t="n">
-        <v>6808338</v>
+        <v>6808192</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118891025</v>
+        <v>118891168</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500061</v>
+        <v>500091</v>
       </c>
       <c r="R8" t="n">
-        <v>6808195</v>
+        <v>6808221</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118891595</v>
+        <v>118891402</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499929</v>
+        <v>500118</v>
       </c>
       <c r="R9" t="n">
-        <v>6808532</v>
+        <v>6808352</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118891497</v>
+        <v>118891776</v>
       </c>
       <c r="B10" t="n">
-        <v>8416</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500086</v>
+        <v>500000</v>
       </c>
       <c r="R10" t="n">
-        <v>6808393</v>
+        <v>6808302</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118891776</v>
+        <v>118891395</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>91786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500000</v>
+        <v>500122</v>
       </c>
       <c r="R11" t="n">
-        <v>6808302</v>
+        <v>6808338</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118891803</v>
+        <v>118891313</v>
       </c>
       <c r="B12" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499999</v>
+        <v>500158</v>
       </c>
       <c r="R12" t="n">
-        <v>6808280</v>
+        <v>6808271</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118891338</v>
+        <v>118891390</v>
       </c>
       <c r="B13" t="n">
-        <v>91779</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500148</v>
+        <v>500123</v>
       </c>
       <c r="R13" t="n">
-        <v>6808267</v>
+        <v>6808319</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118891168</v>
+        <v>118891422</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500091</v>
+        <v>500103</v>
       </c>
       <c r="R14" t="n">
-        <v>6808221</v>
+        <v>6808366</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118891390</v>
+        <v>118890866</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>91790</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,38 +2018,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jussinjärv (Jussinjärv), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500123</v>
+        <v>500089</v>
       </c>
       <c r="R15" t="n">
-        <v>6808319</v>
+        <v>6808108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
         <v>118890625</v>
       </c>
       <c r="B16" t="n">
-        <v>79469</v>
+        <v>79476</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118890866</v>
+        <v>118891375</v>
       </c>
       <c r="B17" t="n">
-        <v>91783</v>
+        <v>91786</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,38 +2242,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500089</v>
+        <v>500143</v>
       </c>
       <c r="R17" t="n">
-        <v>6808108</v>
+        <v>6808303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118891313</v>
+        <v>118891134</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>78228</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500158</v>
+        <v>500077</v>
       </c>
       <c r="R18" t="n">
-        <v>6808271</v>
+        <v>6808223</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118891906</v>
+        <v>118891384</v>
       </c>
       <c r="B19" t="n">
-        <v>90524</v>
+        <v>78491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500003</v>
+        <v>500131</v>
       </c>
       <c r="R19" t="n">
-        <v>6808192</v>
+        <v>6808303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118891402</v>
+        <v>118891442</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
+        <v>78136</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500118</v>
+        <v>500091</v>
       </c>
       <c r="R20" t="n">
-        <v>6808352</v>
+        <v>6808386</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118891442</v>
+        <v>118891025</v>
       </c>
       <c r="B21" t="n">
-        <v>78129</v>
+        <v>78491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500091</v>
+        <v>500061</v>
       </c>
       <c r="R21" t="n">
-        <v>6808386</v>
+        <v>6808195</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118891426</v>
+        <v>118891595</v>
       </c>
       <c r="B22" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500103</v>
+        <v>499929</v>
       </c>
       <c r="R22" t="n">
-        <v>6808366</v>
+        <v>6808532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118891134</v>
+        <v>118891803</v>
       </c>
       <c r="B23" t="n">
-        <v>78221</v>
+        <v>78228</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500077</v>
+        <v>499999</v>
       </c>
       <c r="R23" t="n">
-        <v>6808223</v>
+        <v>6808280</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118891384</v>
+        <v>118891338</v>
       </c>
       <c r="B24" t="n">
-        <v>78484</v>
+        <v>91786</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2956,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500131</v>
+        <v>500148</v>
       </c>
       <c r="R24" t="n">
-        <v>6808303</v>
+        <v>6808267</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3049,7 +3049,7 @@
         <v>118891483</v>
       </c>
       <c r="B25" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118891375</v>
+        <v>118891497</v>
       </c>
       <c r="B26" t="n">
-        <v>91779</v>
+        <v>8416</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,21 +3164,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500143</v>
+        <v>500086</v>
       </c>
       <c r="R26" t="n">
-        <v>6808303</v>
+        <v>6808393</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3253,7 +3253,7 @@
         <v>118890986</v>
       </c>
       <c r="B27" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118891422</v>
+        <v>118891426</v>
       </c>
       <c r="B28" t="n">
-        <v>78220</v>
+        <v>78228</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>

--- a/artfynd/A 48359-2023 artfynd.xlsx
+++ b/artfynd/A 48359-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118891617</v>
+        <v>118891677</v>
       </c>
       <c r="B4" t="n">
-        <v>78491</v>
+        <v>90531</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499837</v>
+        <v>499813</v>
       </c>
       <c r="R4" t="n">
-        <v>6808476</v>
+        <v>6808453</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118891677</v>
+        <v>118891617</v>
       </c>
       <c r="B5" t="n">
-        <v>90531</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499813</v>
+        <v>499837</v>
       </c>
       <c r="R5" t="n">
-        <v>6808453</v>
+        <v>6808476</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118891906</v>
+        <v>118891168</v>
       </c>
       <c r="B7" t="n">
-        <v>90531</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500003</v>
+        <v>500091</v>
       </c>
       <c r="R7" t="n">
-        <v>6808192</v>
+        <v>6808221</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118891168</v>
+        <v>118891402</v>
       </c>
       <c r="B8" t="n">
         <v>78491</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500091</v>
+        <v>500118</v>
       </c>
       <c r="R8" t="n">
-        <v>6808221</v>
+        <v>6808352</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118891402</v>
+        <v>118891906</v>
       </c>
       <c r="B9" t="n">
-        <v>78491</v>
+        <v>90531</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500118</v>
+        <v>500003</v>
       </c>
       <c r="R9" t="n">
-        <v>6808352</v>
+        <v>6808192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 48359-2023 artfynd.xlsx
+++ b/artfynd/A 48359-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118891631</v>
+        <v>118891617</v>
       </c>
       <c r="B2" t="n">
         <v>78491</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499913</v>
+        <v>499837</v>
       </c>
       <c r="R2" t="n">
-        <v>6808448</v>
+        <v>6808476</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118891606</v>
+        <v>118891663</v>
       </c>
       <c r="B3" t="n">
-        <v>78491</v>
+        <v>8416</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499877</v>
+        <v>499858</v>
       </c>
       <c r="R3" t="n">
-        <v>6808544</v>
+        <v>6808367</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118891617</v>
+        <v>118891631</v>
       </c>
       <c r="B5" t="n">
         <v>78491</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499837</v>
+        <v>499913</v>
       </c>
       <c r="R5" t="n">
-        <v>6808476</v>
+        <v>6808448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118891663</v>
+        <v>118891606</v>
       </c>
       <c r="B6" t="n">
-        <v>8416</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,43 +1100,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499858</v>
+        <v>499877</v>
       </c>
       <c r="R6" t="n">
-        <v>6808367</v>
+        <v>6808544</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118891168</v>
+        <v>118891426</v>
       </c>
       <c r="B7" t="n">
-        <v>78491</v>
+        <v>78228</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500091</v>
+        <v>500103</v>
       </c>
       <c r="R7" t="n">
-        <v>6808221</v>
+        <v>6808366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118891402</v>
+        <v>118890866</v>
       </c>
       <c r="B8" t="n">
-        <v>78491</v>
+        <v>91790</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jussinjärv (Jussinjärv), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500118</v>
+        <v>500089</v>
       </c>
       <c r="R8" t="n">
-        <v>6808352</v>
+        <v>6808108</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118891906</v>
+        <v>118891338</v>
       </c>
       <c r="B9" t="n">
-        <v>90531</v>
+        <v>91786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500003</v>
+        <v>500148</v>
       </c>
       <c r="R9" t="n">
-        <v>6808192</v>
+        <v>6808267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118891776</v>
+        <v>118891390</v>
       </c>
       <c r="B10" t="n">
         <v>78491</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500000</v>
+        <v>500123</v>
       </c>
       <c r="R10" t="n">
-        <v>6808302</v>
+        <v>6808319</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118891395</v>
+        <v>118891803</v>
       </c>
       <c r="B11" t="n">
-        <v>91786</v>
+        <v>78228</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500122</v>
+        <v>499999</v>
       </c>
       <c r="R11" t="n">
-        <v>6808338</v>
+        <v>6808280</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118891313</v>
+        <v>118891776</v>
       </c>
       <c r="B12" t="n">
         <v>78491</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500158</v>
+        <v>500000</v>
       </c>
       <c r="R12" t="n">
-        <v>6808271</v>
+        <v>6808302</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118891390</v>
+        <v>118891595</v>
       </c>
       <c r="B13" t="n">
         <v>78491</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500123</v>
+        <v>499929</v>
       </c>
       <c r="R13" t="n">
-        <v>6808319</v>
+        <v>6808532</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118891422</v>
+        <v>118891483</v>
       </c>
       <c r="B14" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500103</v>
+        <v>500089</v>
       </c>
       <c r="R14" t="n">
-        <v>6808366</v>
+        <v>6808383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118890866</v>
+        <v>118890625</v>
       </c>
       <c r="B15" t="n">
-        <v>91790</v>
+        <v>79476</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4365</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500089</v>
+        <v>500110</v>
       </c>
       <c r="R15" t="n">
-        <v>6808108</v>
+        <v>6808019</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,6 +2092,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2108,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118890625</v>
+        <v>118891313</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>78491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,38 +2140,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Jussinjärv (Jussinjärv), Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500110</v>
+        <v>500158</v>
       </c>
       <c r="R16" t="n">
-        <v>6808019</v>
+        <v>6808271</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,26 +2214,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118891375</v>
+        <v>118891497</v>
       </c>
       <c r="B17" t="n">
-        <v>91786</v>
+        <v>8416</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500143</v>
+        <v>500086</v>
       </c>
       <c r="R17" t="n">
-        <v>6808303</v>
+        <v>6808393</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118891134</v>
+        <v>118891168</v>
       </c>
       <c r="B18" t="n">
-        <v>78228</v>
+        <v>78491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500077</v>
+        <v>500091</v>
       </c>
       <c r="R18" t="n">
-        <v>6808223</v>
+        <v>6808221</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118891442</v>
+        <v>118891395</v>
       </c>
       <c r="B20" t="n">
-        <v>78136</v>
+        <v>91786</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,25 +2548,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500091</v>
+        <v>500122</v>
       </c>
       <c r="R20" t="n">
-        <v>6808386</v>
+        <v>6808338</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118891025</v>
+        <v>118891134</v>
       </c>
       <c r="B21" t="n">
-        <v>78491</v>
+        <v>78228</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500061</v>
+        <v>500077</v>
       </c>
       <c r="R21" t="n">
-        <v>6808195</v>
+        <v>6808223</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118891595</v>
+        <v>118891442</v>
       </c>
       <c r="B22" t="n">
-        <v>78491</v>
+        <v>78136</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499929</v>
+        <v>500091</v>
       </c>
       <c r="R22" t="n">
-        <v>6808532</v>
+        <v>6808386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118891803</v>
+        <v>118891906</v>
       </c>
       <c r="B23" t="n">
-        <v>78228</v>
+        <v>90531</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499999</v>
+        <v>500003</v>
       </c>
       <c r="R23" t="n">
-        <v>6808280</v>
+        <v>6808192</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118891338</v>
+        <v>118891402</v>
       </c>
       <c r="B24" t="n">
-        <v>91786</v>
+        <v>78491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2956,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500148</v>
+        <v>500118</v>
       </c>
       <c r="R24" t="n">
-        <v>6808267</v>
+        <v>6808352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118891483</v>
+        <v>118891375</v>
       </c>
       <c r="B25" t="n">
-        <v>78491</v>
+        <v>91786</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,25 +3058,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500089</v>
+        <v>500143</v>
       </c>
       <c r="R25" t="n">
-        <v>6808383</v>
+        <v>6808303</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118891497</v>
+        <v>118891422</v>
       </c>
       <c r="B26" t="n">
-        <v>8416</v>
+        <v>78227</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3160,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500086</v>
+        <v>500103</v>
       </c>
       <c r="R26" t="n">
-        <v>6808393</v>
+        <v>6808366</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118890986</v>
+        <v>118891025</v>
       </c>
       <c r="B27" t="n">
-        <v>90531</v>
+        <v>78491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,21 +3266,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500050</v>
+        <v>500061</v>
       </c>
       <c r="R27" t="n">
-        <v>6808191</v>
+        <v>6808195</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118891426</v>
+        <v>118890986</v>
       </c>
       <c r="B28" t="n">
-        <v>78228</v>
+        <v>90531</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500103</v>
+        <v>500050</v>
       </c>
       <c r="R28" t="n">
-        <v>6808366</v>
+        <v>6808191</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
